--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2022/MONTANA_2022.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2022/MONTANA_2022.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D137"/>
+  <dimension ref="A1:D131"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Calvillo</t>
@@ -408,6 +413,11 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>Jesús María</t>
@@ -421,6 +431,11 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>Total</t>
@@ -452,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Baja California Sur</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Mulegé</t>
@@ -465,6 +485,11 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Baja California Sur</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>Total</t>
@@ -496,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Carmen</t>
@@ -509,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Total</t>
@@ -540,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Frontera Comalapa</t>
@@ -553,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Ocosingo</t>
@@ -566,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Tonalá</t>
@@ -579,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Villa Corzo</t>
@@ -592,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Total</t>
@@ -623,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Chihuahua</t>
@@ -636,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Delicias</t>
@@ -649,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Janos</t>
@@ -662,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Saucillo</t>
@@ -675,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Temósachic</t>
@@ -688,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Total</t>
@@ -719,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Total</t>
@@ -734,7 +829,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -750,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -763,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -776,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -789,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Total</t>
@@ -820,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>San Dimas</t>
@@ -833,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Total</t>
@@ -848,7 +973,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -864,9 +989,14 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>San Felipe del Progreso</t>
+          <t>San Felipe Del Progreso</t>
         </is>
       </c>
       <c r="C36">
@@ -877,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Temascalcingo</t>
@@ -890,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -903,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Tultitlán</t>
@@ -916,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Villa Guerrero</t>
@@ -929,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Total</t>
@@ -949,7 +1104,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Apaseo el Alto</t>
+          <t>Apaseo El Alto</t>
         </is>
       </c>
       <c r="C42">
@@ -960,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Celaya</t>
@@ -973,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Doctor Mora</t>
@@ -986,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>León</t>
@@ -999,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Pénjamo</t>
@@ -1012,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Romita</t>
@@ -1025,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Salvatierra</t>
@@ -1038,9 +1223,14 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>San Luis de la Paz</t>
+          <t>San Luis De La Paz</t>
         </is>
       </c>
       <c r="C49">
@@ -1051,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1071,7 +1266,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Chilpancingo de los Bravo</t>
+          <t>Chilpancingo De Los Bravo</t>
         </is>
       </c>
       <c r="C51">
@@ -1082,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Cocula</t>
@@ -1095,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Eduardo Neri</t>
@@ -1108,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>General Heliodoro Castillo</t>
@@ -1121,9 +1331,14 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Huitzuco de los Figueroa</t>
+          <t>Huitzuco De Los Figueroa</t>
         </is>
       </c>
       <c r="C55">
@@ -1134,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>San Luis Acatlán</t>
@@ -1147,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Tecoanapa</t>
@@ -1160,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1191,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Calnali</t>
@@ -1204,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Epazoyucan</t>
@@ -1217,9 +1457,14 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Pachuca de Soto</t>
+          <t>Pachuca De Soto</t>
         </is>
       </c>
       <c r="C62">
@@ -1230,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Zimapán</t>
@@ -1243,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1263,7 +1518,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Autlán de Navarro</t>
+          <t>Autlán De Navarro</t>
         </is>
       </c>
       <c r="C65">
@@ -1274,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Casimiro Castillo</t>
@@ -1287,6 +1547,11 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -1300,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>San Julián</t>
@@ -1313,6 +1583,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Villa Purificación</t>
@@ -1326,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Zapopan</t>
@@ -1339,9 +1619,14 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Zapotlán el Grande</t>
+          <t>Zapotlán El Grande</t>
         </is>
       </c>
       <c r="C71">
@@ -1352,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1383,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Zamora</t>
@@ -1396,6 +1691,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1427,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1458,6 +1763,11 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1478,7 +1788,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>San Nicolás de los Garza</t>
+          <t>San Nicolás De Los Garza</t>
         </is>
       </c>
       <c r="C80">
@@ -1489,6 +1799,11 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1509,7 +1824,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Oaxaca de Juárez</t>
+          <t>Oaxaca De Juárez</t>
         </is>
       </c>
       <c r="C82">
@@ -1520,9 +1835,14 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Pinotepa de Don Luis</t>
+          <t>Pinotepa De Don Luis</t>
         </is>
       </c>
       <c r="C83">
@@ -1533,9 +1853,14 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Villa de Tututepec de Melchor Ocampo</t>
+          <t>Villa De Tututepec De Melchor Ocampo</t>
         </is>
       </c>
       <c r="C84">
@@ -1546,6 +1871,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1577,6 +1907,11 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>San Pablo Anicano</t>
@@ -1590,9 +1925,14 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Tepexi de Rodríguez</t>
+          <t>Tepexi De Rodríguez</t>
         </is>
       </c>
       <c r="C88">
@@ -1603,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1623,7 +1968,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Amealco de Bonfil</t>
+          <t>Amealco De Bonfil</t>
         </is>
       </c>
       <c r="C90">
@@ -1634,6 +1979,11 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>El Marqués</t>
@@ -1647,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Querétaro</t>
@@ -1660,6 +2015,11 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1691,9 +2051,14 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Mexquitic de Carmona</t>
+          <t>Mexquitic De Carmona</t>
         </is>
       </c>
       <c r="C95">
@@ -1704,6 +2069,11 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>San Luis Potosí</t>
@@ -1717,6 +2087,11 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>San Nicolás Tolentino</t>
@@ -1730,9 +2105,14 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Villa de Ramos</t>
+          <t>Villa De Ramos</t>
         </is>
       </c>
       <c r="C98">
@@ -1743,6 +2123,11 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1774,6 +2159,11 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>Culiacán</t>
@@ -1787,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>Mocorito</t>
@@ -1800,6 +2195,11 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1831,6 +2231,11 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1862,6 +2267,11 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1893,6 +2303,11 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1924,6 +2339,11 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1955,6 +2375,11 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>Alpatláhuac</t>
@@ -1968,6 +2393,11 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>Calcahualco</t>
@@ -1981,6 +2411,11 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>Chacaltianguis</t>
@@ -1994,6 +2429,11 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>Coscomatepec</t>
@@ -2007,6 +2447,11 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>Hidalgotitlán</t>
@@ -2020,6 +2465,11 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>Jesús Carranza</t>
@@ -2033,6 +2483,11 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>Nautla</t>
@@ -2046,6 +2501,11 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>Xalapa</t>
@@ -2059,6 +2519,11 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>Zongolica</t>
@@ -2072,6 +2537,11 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2103,6 +2573,11 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2134,9 +2609,14 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Concepción del Oro</t>
+          <t>Concepción Del Oro</t>
         </is>
       </c>
       <c r="C126">
@@ -2147,6 +2627,11 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>General Pánfilo Natera</t>
@@ -2160,6 +2645,11 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>Miguel Auza</t>
@@ -2173,6 +2663,11 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>Ojocaliente</t>
@@ -2186,6 +2681,11 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2209,41 +2709,6 @@
       </c>
       <c r="D131">
         <v>1</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 566,547</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Mayo de 2023</t>
-        </is>
       </c>
     </row>
   </sheetData>
